--- a/com.zerogamestudio.zeroengine.config-pipeline/Samples~/MinimalItemDrop/Config/drops.xlsx
+++ b/com.zerogamestudio.zeroengine.config-pipeline/Samples~/MinimalItemDrop/Config/drops.xlsx
@@ -1,38 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:bookViews>
+    <x:workbookView firstSheet="3" activeTab="3"/>
+  </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_zgs_schema" sheetId="1" state="visible" r:id="Rdb12d834976343f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_zgs_meta" sheetId="2" state="veryHidden" r:id="R3420dbcfaeba4e9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_zgs_lists" sheetId="3" state="veryHidden" r:id="Rf148140f6fdc4025"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropTables" sheetId="4" state="visible" r:id="Re051491ae573470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropEntries" sheetId="5" state="visible" r:id="Re8f9a2f728734237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_zgs_schema" sheetId="1" state="veryHidden" r:id="Re3fc99b2fe514d4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_zgs_meta" sheetId="2" state="veryHidden" r:id="Re31b2df30d114ef4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_zgs_lists" sheetId="3" state="veryHidden" r:id="R0deb6d9516ab4b1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="4" state="visible" r:id="R80ce806406cd444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropTables" sheetId="5" state="visible" r:id="Rf2b3e4aef6404cce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropEntries" sheetId="6" state="visible" r:id="Re2978ae9addf4e87"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="6">
     <x:font/>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:color rgb="FFFFFFFF"/>
+    </x:font>
+    <x:font>
+      <x:u/>
+      <x:color rgb="FF0563C1"/>
+    </x:font>
+    <x:font>
+      <x:color rgb="FF666666"/>
+    </x:font>
+    <x:font>
+      <x:u/>
+      <x:color rgb="FFFFFFFF"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="2">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf/>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="10">
     <x:xf/>
     <x:xf applyProtection="1">
+      <x:protection locked="0"/>
+    </x:xf>
+    <x:xf fontId="1" fillId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf fontId="4" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf fontId="3" borderId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf borderId="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf fontId="2" fillId="2" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf fontId="5" fillId="2" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="49" applyNumberFormat="1" applyProtection="1">
       <x:protection locked="0"/>
     </x:xf>
   </x:cellXfs>
@@ -44,316 +119,340 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ZGS_DropTables_1" displayName="ZGS_DropTables_1" ref="A2:A3" totalsRowShown="0">
+  <x:autoFilter ref="A2:A3"/>
+  <x:tableColumns count="1">
+    <x:tableColumn id="1" name="← 配置目录 ｜ ＊ 掉落表 ID"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ZGS_DropEntries_2" displayName="ZGS_DropEntries_2" ref="A2:E3" totalsRowShown="0">
+  <x:autoFilter ref="A2:E3"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="← 配置目录 ｜ ＊ dropTableId（关联键，不导出）"/>
+    <x:tableColumn id="2" name="＊ 条目 ID"/>
+    <x:tableColumn id="3" name="＊ 顺序"/>
+    <x:tableColumn id="4" name="＊ 物品 ID"/>
+    <x:tableColumn id="5" name="＊ 概率"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+    <x:row r="1">
+      <x:c r="A1" s="0" t="inlineStr">
         <x:is>
           <x:t>Sheet</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B1" s="0" t="inlineStr">
         <x:is>
           <x:t>Field</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="C1" s="0" t="inlineStr">
         <x:is>
           <x:t>Title</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="D1" s="0" t="inlineStr">
         <x:is>
           <x:t>Type</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="E1" s="0" t="inlineStr">
         <x:is>
           <x:t>Required</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="F1" s="0" t="inlineStr">
         <x:is>
           <x:t>Default</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="G1" s="0" t="inlineStr">
         <x:is>
           <x:t>Range/Enum</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="H1" s="0" t="inlineStr">
         <x:is>
           <x:t>Reference</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="I1" s="0" t="inlineStr">
         <x:is>
           <x:t>Unit</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="J1" s="0" t="inlineStr">
         <x:is>
           <x:t>Description</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+    <x:row r="2">
+      <x:c r="A2" s="0" t="inlineStr">
         <x:is>
           <x:t>DropTables</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B2" s="0" t="inlineStr">
         <x:is>
           <x:t>id</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="C2" s="0" t="inlineStr">
         <x:is>
           <x:t>掉落表 ID</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="D2" s="0" t="inlineStr">
         <x:is>
           <x:t>string</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="E2" s="0" t="inlineStr">
         <x:is>
           <x:t>yes</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="F2" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="G2" s="0" t="inlineStr">
         <x:is>
           <x:t>..</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+      <x:c r="H2" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="I2" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="J2" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="0" t="inlineStr">
         <x:is>
           <x:t>DropEntries</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B3" s="0" t="inlineStr">
         <x:is>
           <x:t>id</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="C3" s="0" t="inlineStr">
         <x:is>
           <x:t>条目 ID</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="D3" s="0" t="inlineStr">
         <x:is>
           <x:t>string</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="E3" s="0" t="inlineStr">
         <x:is>
           <x:t>yes</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="F3" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="0" t="inlineStr">
         <x:is>
           <x:t>..</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+      <x:c r="H3" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="I3" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="J3" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="0" t="inlineStr">
         <x:is>
           <x:t>DropEntries</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B4" s="0" t="inlineStr">
         <x:is>
           <x:t>order</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="C4" s="0" t="inlineStr">
         <x:is>
           <x:t>顺序</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="D4" s="0" t="inlineStr">
         <x:is>
           <x:t>int32</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="E4" s="0" t="inlineStr">
         <x:is>
           <x:t>yes</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="F4" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="G4" s="0" t="inlineStr">
         <x:is>
           <x:t>0..</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+      <x:c r="H4" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="I4" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="J4" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="0" t="inlineStr">
         <x:is>
           <x:t>DropEntries</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B5" s="0" t="inlineStr">
         <x:is>
           <x:t>itemId</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="C5" s="0" t="inlineStr">
         <x:is>
           <x:t>物品 ID</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="D5" s="0" t="inlineStr">
         <x:is>
           <x:t>string</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="E5" s="0" t="inlineStr">
         <x:is>
           <x:t>yes</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="F5" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="0" t="inlineStr">
         <x:is>
           <x:t>..</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="H5" s="0" t="inlineStr">
         <x:is>
           <x:t>#/properties/items/items/properties/id</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+      <x:c r="I5" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="J5" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="0" t="inlineStr">
         <x:is>
           <x:t>DropEntries</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B6" s="0" t="inlineStr">
         <x:is>
           <x:t>chance</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="C6" s="0" t="inlineStr">
         <x:is>
           <x:t>概率</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="D6" s="0" t="inlineStr">
         <x:is>
           <x:t>float32</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="E6" s="0" t="inlineStr">
         <x:is>
           <x:t>yes</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="F6" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="0" t="inlineStr">
         <x:is>
           <x:t>0..1</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="H6" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="I6" s="0" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="J6" s="0" t="inlineStr">
         <x:is>
           <x:t/>
         </x:is>
@@ -367,75 +466,75 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+    <x:row r="1">
+      <x:c r="A1" s="0" t="inlineStr">
         <x:is>
           <x:t>toolFormatVersion</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B1" s="0" t="inlineStr">
+        <x:is>
+          <x:t>2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="0" t="inlineStr">
+        <x:is>
+          <x:t>schemaId</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="0" t="inlineStr">
+        <x:is>
+          <x:t>urn:zgs:sample:item-drop</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="0" t="inlineStr">
+        <x:is>
+          <x:t>schemaVersion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="0" t="inlineStr">
         <x:is>
           <x:t>1</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t>schemaId</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t>urn:zgs:sample:item-drop</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t>schemaVersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t>1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+    <x:row r="4">
+      <x:c r="A4" s="0" t="inlineStr">
         <x:is>
           <x:t>schemaHash</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B4" s="0" t="inlineStr">
         <x:is>
           <x:t>801aa05b1218a88778517f78eecb6dc2fbf97b00466181dc80ad2d112b314815</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+    <x:row r="5">
+      <x:c r="A5" s="0" t="inlineStr">
         <x:is>
           <x:t>configSetId</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
+      <x:c r="B5" s="0" t="inlineStr">
         <x:is>
           <x:t>sample.item-drop</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row>
-      <x:c s="0" t="inlineStr">
+    <x:row r="6">
+      <x:c r="A6" s="0" t="inlineStr">
         <x:is>
           <x:t>workbookBaseHash</x:t>
         </x:is>
       </x:c>
-      <x:c s="0" t="inlineStr">
-        <x:is>
-          <x:t>13255d23d0c392d6225b9b13be78d2981385d99ee84681ff7aaaadc8ee1e7cd7</x:t>
+      <x:c r="B6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>f76e669736ac0938cd65fc4954e4cbfb239fcc50b451d5023fac68d66b3e845d</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -454,7 +553,114 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:cols>
-    <x:col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="24" customWidth="1"/>
+    <x:col min="2" max="2" width="28" customWidth="1"/>
+    <x:col min="3" max="3" width="56" customWidth="1"/>
+    <x:col min="4" max="4" width="12" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="2" t="inlineStr">
+        <x:is>
+          <x:t>配置目录</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="3" t="inlineStr">
+        <x:is>
+          <x:t>点击 Sheet 名称进入配置；保存后回 Unity 执行 Check / Plan / Apply。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="3" t="inlineStr">
+        <x:is>
+          <x:t>说明：标注“仅策划，不导出”或“关联键，不导出”的列不会进入运行时 JSON / DTO。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="4" t="inlineStr">
+        <x:is>
+          <x:t>配置模块</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="4" t="inlineStr">
+        <x:is>
+          <x:t>Sheet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="4" t="inlineStr">
+        <x:is>
+          <x:t>说明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="4" t="inlineStr">
+        <x:is>
+          <x:t>字段数</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" s="6" t="inlineStr">
+        <x:is>
+          <x:t>dropTables</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="5" t="inlineStr">
+        <x:is>
+          <x:t>DropTables</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="6" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="6" t="inlineStr">
+        <x:is>
+          <x:t>entries</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="5" t="inlineStr">
+        <x:is>
+          <x:t>DropEntries</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="6" t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:sheetProtection sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <x:autoFilter ref="A4:D6"/>
+  <x:mergeCells count="3">
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A3:D3"/>
+  </x:mergeCells>
+  <x:hyperlinks>
+    <x:hyperlink ref="B5" location="'DropTables'!A2" display="DropTables"/>
+    <x:hyperlink ref="B6" location="'DropEntries'!A2" display="DropEntries"/>
+  </x:hyperlinks>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:cols>
+    <x:col min="1" max="1" width="28" style="9" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" hidden="1">
@@ -464,30 +670,38 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>掉落表 ID</x:t>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="8" t="inlineStr">
+        <x:is>
+          <x:t>← 配置目录 ｜ ＊ 掉落表 ID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1" t="inlineStr">
+      <x:c r="A3" s="9" t="inlineStr">
         <x:is>
           <x:t>drop.starter</x:t>
         </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:sheetProtection sheet="1" objects="1" scenarios="1" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <x:autoFilter ref="A2:A2"/>
+  <x:hyperlinks>
+    <x:hyperlink ref="A2" location="'配置目录'!A1" display="← 配置目录"/>
+  </x:hyperlinks>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b04fa08ba384232"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:cols>
-    <x:col min="1" max="5" width="18" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="28" style="9" customWidth="1"/>
+    <x:col min="2" max="2" width="28" style="9" customWidth="1"/>
+    <x:col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="22" style="9" customWidth="1"/>
+    <x:col min="5" max="5" width="15" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" hidden="1">
@@ -517,40 +731,40 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>dropTableId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>条目 ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>顺序</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>物品 ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>概率</x:t>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="8" t="inlineStr">
+        <x:is>
+          <x:t>← 配置目录 ｜ ＊ dropTableId（关联键，不导出）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="7" t="inlineStr">
+        <x:is>
+          <x:t>＊ 条目 ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="7" t="inlineStr">
+        <x:is>
+          <x:t>＊ 顺序</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="7" t="inlineStr">
+        <x:is>
+          <x:t>＊ 物品 ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="7" t="inlineStr">
+        <x:is>
+          <x:t>＊ 概率</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1" t="inlineStr">
+      <x:c r="A3" s="9" t="inlineStr">
         <x:is>
           <x:t>drop.starter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="1" t="inlineStr">
+      <x:c r="B3" s="9" t="inlineStr">
         <x:is>
           <x:t>entry.coin</x:t>
         </x:is>
@@ -558,7 +772,7 @@
       <x:c r="C3" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="inlineStr">
+      <x:c r="D3" s="9" t="inlineStr">
         <x:is>
           <x:t>item.coin</x:t>
         </x:is>
@@ -568,7 +782,20 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:sheetProtection sheet="1" objects="1" scenarios="1" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <x:autoFilter ref="A2:E2"/>
+  <x:dataValidations count="2">
+    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="配置值无效" error="请按字段约束输入；保存后仍需执行 Check。" promptTitle="顺序" prompt="必填；请输入符合范围的数值。" sqref="C3:C1048576">
+      <x:formula1>0</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="配置值无效" error="请按字段约束输入；保存后仍需执行 Check。" promptTitle="概率" prompt="必填；请输入符合范围的数值。" sqref="E3:E1048576">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:hyperlinks>
+    <x:hyperlink ref="A2" location="'配置目录'!A1" display="← 配置目录"/>
+  </x:hyperlinks>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06219a2cffbe4318"/>
+  </x:tableParts>
 </x:worksheet>
 </file>